--- a/dh-module-oa/dh-module-oa-server/src/main/resources/excel-templates/印章使用申请单.xlsx
+++ b/dh-module-oa/dh-module-oa-server/src/main/resources/excel-templates/印章使用申请单.xlsx
@@ -1,41 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\aLJD\server\oa\dh-oa\dh-module-oa\dh-module-oa-server\src\main\resources\excel-templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{732EECDE-22BA-4AA8-BAA1-7242BA64D33A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE4C3966-84BD-4BF7-B12C-F4D032910E45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="3015" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>秘书处印鉴使用申请单</t>
   </si>
   <si>
+    <t xml:space="preserve">申请人：{creatorName}      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                              编号：</t>
+  </si>
+  <si>
+    <t>{billCode}</t>
+  </si>
+  <si>
     <t>日 期</t>
   </si>
   <si>
@@ -48,50 +46,31 @@
     <t>印鉴种类</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t xml:space="preserve">                              编号：</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">申请人：{creatorName}      </t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>{billCode}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>{year}年{month}月{day}日</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>{destinationUnit}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>{sealName}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>{documentCount}</t>
+  </si>
+  <si>
+    <t>用 印 事 由</t>
   </si>
   <si>
     <t>{cause}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>用 印 事 由</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>印鉴管理人:</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>审核:</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>批准:</t>
+  </si>
+  <si>
+    <t>{sealTypeName}</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -152,7 +131,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -176,19 +155,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -227,69 +193,56 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -569,142 +522,120 @@
   <dimension ref="A1:E9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="14.125" customWidth="1"/>
-    <col min="3" max="3" width="27.625" customWidth="1"/>
-    <col min="4" max="4" width="8.625" customWidth="1"/>
-    <col min="5" max="5" width="19.625" customWidth="1"/>
+    <col min="1" max="2" width="14.125" style="7" customWidth="1"/>
+    <col min="3" max="3" width="27.625" style="7" customWidth="1"/>
+    <col min="4" max="4" width="8.625" style="7" customWidth="1"/>
+    <col min="5" max="5" width="19.625" style="7" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
     </row>
     <row r="2" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="12"/>
+      <c r="C2" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="12"/>
+      <c r="E2" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="9"/>
+      <c r="C3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="13"/>
-      <c r="E2" s="4" t="s">
+    </row>
+    <row r="4" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="8" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="15" t="s">
+      <c r="B4" s="9"/>
+      <c r="C4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="16" t="s">
+      <c r="D4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="17" t="s">
+      <c r="E4" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="17" t="s">
-        <v>13</v>
       </c>
       <c r="B5" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="9"/>
     </row>
     <row r="6" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="9"/>
+      <c r="C6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="20" t="s">
+      <c r="D6" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="19" t="s">
-        <v>16</v>
-      </c>
       <c r="E6" s="9"/>
     </row>
     <row r="7" spans="1:5" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="12"/>
+      <c r="A7" s="14"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="9"/>
     </row>
     <row r="8" spans="1:5" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>5</v>
-      </c>
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
     </row>
     <row r="9" spans="1:5" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>5</v>
-      </c>
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
     <mergeCell ref="A7:E7"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="D6:E6"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.39370078740157499" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>

--- a/dh-module-oa/dh-module-oa-server/src/main/resources/excel-templates/印章使用申请单.xlsx
+++ b/dh-module-oa/dh-module-oa-server/src/main/resources/excel-templates/印章使用申请单.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\aLJD\server\oa\dh-oa\dh-module-oa\dh-module-oa-server\src\main\resources\excel-templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE4C3966-84BD-4BF7-B12C-F4D032910E45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDADDF97-E7D8-4E93-9CE5-57BB62D4B9EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="3015" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,9 +28,6 @@
     <t xml:space="preserve">申请人：{creatorName}      </t>
   </si>
   <si>
-    <t xml:space="preserve">                              编号：</t>
-  </si>
-  <si>
     <t>{billCode}</t>
   </si>
   <si>
@@ -71,6 +68,10 @@
   </si>
   <si>
     <t>{sealTypeName}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>编号：</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -193,7 +194,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -203,37 +204,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -244,6 +235,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -522,94 +520,94 @@
   <dimension ref="A1:E9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="14.125" style="7" customWidth="1"/>
-    <col min="3" max="3" width="27.625" style="7" customWidth="1"/>
-    <col min="4" max="4" width="8.625" style="7" customWidth="1"/>
-    <col min="5" max="5" width="19.625" style="7" customWidth="1"/>
+    <col min="1" max="2" width="14.125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="27.625" style="6" customWidth="1"/>
+    <col min="4" max="4" width="8.625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="19.625" style="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
     </row>
     <row r="2" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="13" t="s">
+      <c r="B2" s="18"/>
+      <c r="C2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="12"/>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="11"/>
+    </row>
+    <row r="3" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="15" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="19" t="s">
+      <c r="B3" s="10"/>
+      <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="9"/>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="1" t="s">
+    </row>
+    <row r="4" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="17" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="8" t="s">
+      <c r="B4" s="10"/>
+      <c r="C4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
+      <c r="B5" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="10"/>
+    </row>
+    <row r="6" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="9"/>
-    </row>
-    <row r="6" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="10" t="s">
+      <c r="B6" s="10"/>
+      <c r="C6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="9"/>
+      <c r="E6" s="10"/>
     </row>
     <row r="7" spans="1:5" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="14"/>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="9"/>
+      <c r="A7" s="8"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="10"/>
     </row>
     <row r="8" spans="1:5" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
@@ -627,6 +625,8 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="D2:E2"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="A3:B3"/>
@@ -634,8 +634,6 @@
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.39370078740157499" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
